--- a/data/trans_orig/IP07C16-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C16-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 89,29%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 89,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21892</t>
+          <t>22177</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>11111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25039</t>
+          <t>25165</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39215</t>
+          <t>39636</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20975</t>
+          <t>20727</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22290</t>
+          <t>22866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36620</t>
+          <t>36337</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,42%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>12965</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>6857</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>17177</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15182</t>
+          <t>14936</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6252</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>14353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14917</t>
+          <t>14985</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26177</t>
+          <t>26508</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16354</t>
+          <t>16194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8836</t>
+          <t>8840</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17306</t>
+          <t>18005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>19345</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31441</t>
+          <t>31420</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,17%</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>737</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15849</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28335</t>
+          <t>27729</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>26490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41228</t>
+          <t>40066</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>16638</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12795</t>
+          <t>12408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23135</t>
+          <t>23375</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23646</t>
+          <t>23442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36809</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,1%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14785</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19270</t>
+          <t>19597</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>709</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25340</t>
+          <t>25352</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39041</t>
+          <t>39229</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26808</t>
+          <t>26347</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40179</t>
+          <t>40694</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55714</t>
+          <t>55876</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75399</t>
+          <t>75771</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,93%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28861</t>
+          <t>28482</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>42676</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26160</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40163</t>
+          <t>40662</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>58484</t>
+          <t>58678</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>80059</t>
+          <t>79210</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19831</t>
+          <t>19465</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16645</t>
+          <t>16091</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17640</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32408</t>
+          <t>32443</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>660</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13669</t>
+          <t>14004</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>24749</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>18636</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31689</t>
+          <t>30939</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>35543</t>
+          <t>35942</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>52683</t>
+          <t>52122</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,13%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16571</t>
+          <t>16348</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27256</t>
+          <t>27466</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>22669</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34626</t>
+          <t>34801</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41391</t>
+          <t>41997</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>58007</t>
+          <t>58120</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11387</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10741</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>22139</t>
+          <t>22079</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11434</t>
+          <t>11262</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21089</t>
+          <t>21530</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>19099</t>
+          <t>19902</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>32387</t>
+          <t>32910</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>47,21%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11097</t>
+          <t>10599</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20612</t>
+          <t>19749</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>15102</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>23816</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28099</t>
+          <t>28627</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>42040</t>
+          <t>41485</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>59,51%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>93059</t>
+          <t>93210</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>117481</t>
+          <t>119631</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>103208</t>
+          <t>103588</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>128287</t>
+          <t>130209</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>202487</t>
+          <t>204237</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>239677</t>
+          <t>241943</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>98630</t>
+          <t>95924</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>123198</t>
+          <t>122825</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>114587</t>
+          <t>113899</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>141696</t>
+          <t>141683</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>221134</t>
+          <t>221296</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>260548</t>
+          <t>258533</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,63%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>29949</t>
+          <t>29876</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>48378</t>
+          <t>48519</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>31452</t>
+          <t>31776</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>49780</t>
+          <t>49712</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>64239</t>
+          <t>65884</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>90421</t>
+          <t>92308</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>13040</t>
+          <t>13797</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>11086</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>20095</t>
+          <t>20228</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 95,2%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 95,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22841</t>
+          <t>23015</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10062</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19026</t>
+          <t>18801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25163</t>
+          <t>25003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38912</t>
+          <t>38573</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,23%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19448</t>
+          <t>19486</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18129</t>
+          <t>18203</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21194</t>
+          <t>21846</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34758</t>
+          <t>35022</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,24%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6069</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15378</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10705</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>19973</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23966</t>
+          <t>23947</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27253</t>
+          <t>27463</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41890</t>
+          <t>40668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>60,06%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18089</t>
+          <t>18208</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>16063</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>18192</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31279</t>
+          <t>30986</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>11559</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15878</t>
+          <t>15160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21252</t>
+          <t>21488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34469</t>
+          <t>34582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15311</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26020</t>
+          <t>25859</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17568</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>26511</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40351</t>
+          <t>40107</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,38%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15819</t>
+          <t>15119</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53310</t>
+          <t>52773</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42281</t>
+          <t>41936</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58185</t>
+          <t>57725</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84684</t>
+          <t>84818</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107551</t>
+          <t>107024</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,25%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>22497</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36579</t>
+          <t>36410</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24068</t>
+          <t>24793</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39650</t>
+          <t>39383</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51319</t>
+          <t>50518</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>72159</t>
+          <t>71941</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4648</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19173</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15183</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29392</t>
+          <t>29675</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3473</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26212</t>
+          <t>25871</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39442</t>
+          <t>39895</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28832</t>
+          <t>28688</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>42148</t>
+          <t>42637</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>58980</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>79097</t>
+          <t>78071</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,44%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26178</t>
+          <t>26865</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40108</t>
+          <t>41071</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23337</t>
+          <t>22754</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>36625</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>53637</t>
+          <t>54037</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>72603</t>
+          <t>73236</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,13%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12538</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11252</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>19739</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11607</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8626</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>18003</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>15155</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>26922</t>
+          <t>27145</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,66%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12166</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21968</t>
+          <t>22127</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17915</t>
+          <t>17826</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>30130</t>
+          <t>29797</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11292</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8995</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>18117</t>
+          <t>17353</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>122144</t>
+          <t>122703</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>150156</t>
+          <t>149930</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>129219</t>
+          <t>130194</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>157715</t>
+          <t>157582</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>258039</t>
+          <t>261640</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>298727</t>
+          <t>298850</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,02%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>104888</t>
+          <t>104767</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>131950</t>
+          <t>131120</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>101831</t>
+          <t>101716</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>130177</t>
+          <t>129586</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>214035</t>
+          <t>213084</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>252632</t>
+          <t>252231</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>25225</t>
+          <t>26322</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>43363</t>
+          <t>44751</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>30878</t>
+          <t>31088</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>49182</t>
+          <t>49157</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>60642</t>
+          <t>62185</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>87635</t>
+          <t>88926</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>12584</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>14569</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23694</t>
+          <t>23576</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23204</t>
+          <t>24030</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30554</t>
+          <t>30489</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44377</t>
+          <t>45089</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>64,37%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15231</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19433</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17278</t>
+          <t>17343</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31558</t>
+          <t>31055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,34%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>10701</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>571</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24055</t>
+          <t>23759</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>15521</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26113</t>
+          <t>26540</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31005</t>
+          <t>30432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46649</t>
+          <t>47582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>49,06%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27061</t>
+          <t>27024</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>16019</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27490</t>
+          <t>26801</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35067</t>
+          <t>34492</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51179</t>
+          <t>51548</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,15%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13540</t>
+          <t>13064</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18889</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13400</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>13010</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23273</t>
+          <t>23429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21067</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33980</t>
+          <t>33840</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,63%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17109</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8827</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>18740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19785</t>
+          <t>19119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32506</t>
+          <t>32045</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8078</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>9841</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>15078</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41853</t>
+          <t>41815</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59646</t>
+          <t>58573</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30513</t>
+          <t>30579</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46895</t>
+          <t>46726</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77005</t>
+          <t>77044</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>101675</t>
+          <t>100021</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29627</t>
+          <t>30430</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46532</t>
+          <t>46545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37432</t>
+          <t>36728</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53369</t>
+          <t>53876</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>72050</t>
+          <t>71958</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>95825</t>
+          <t>95274</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28046</t>
+          <t>27425</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17719</t>
+          <t>18786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23179</t>
+          <t>23274</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41329</t>
+          <t>40179</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22816</t>
+          <t>22861</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36741</t>
+          <t>36654</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26156</t>
+          <t>25589</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40151</t>
+          <t>39331</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>53103</t>
+          <t>52947</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>72804</t>
+          <t>72588</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,31%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27155</t>
+          <t>27647</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42307</t>
+          <t>42419</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19421</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33223</t>
+          <t>32514</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>50128</t>
+          <t>50291</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>70083</t>
+          <t>70879</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>15625</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17204</t>
+          <t>17065</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14527</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>27963</t>
+          <t>27828</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16906</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10961</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21013</t>
+          <t>20783</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20694</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34019</t>
+          <t>34778</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19633</t>
+          <t>19773</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20219</t>
+          <t>19702</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22214</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35661</t>
+          <t>36346</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10521</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>16674</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>660</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>124259</t>
+          <t>123501</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>152837</t>
+          <t>152381</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>129018</t>
+          <t>129584</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>157850</t>
+          <t>159733</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>261205</t>
+          <t>261208</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>304785</t>
+          <t>305030</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>116170</t>
+          <t>115358</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>145353</t>
+          <t>145403</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>121692</t>
+          <t>119238</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>150438</t>
+          <t>149246</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>244498</t>
+          <t>245896</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>286123</t>
+          <t>289731</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>38599</t>
+          <t>38444</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>59671</t>
+          <t>59915</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>33448</t>
+          <t>33268</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>54795</t>
+          <t>53528</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>77315</t>
+          <t>76728</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>106255</t>
+          <t>106811</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>22819</t>
+          <t>22600</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>791</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>784</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
